--- a/data/trans_camb/P1416-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1416-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,6</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,73</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,19</t>
+          <t>-3,16; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,64</t>
+          <t>-3,09; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,28</t>
+          <t>0,96; 6,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 0,75</t>
+          <t>-5,01; 0,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 0,12</t>
+          <t>-5,61; 0,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 6,96</t>
+          <t>0,24; 6,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,49</t>
+          <t>-3,35; 0,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,06</t>
+          <t>-3,62; -0,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,19</t>
+          <t>1,7; 5,82</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 29,84</t>
+          <t>-51,84; 30,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,36; 44,54</t>
+          <t>-46,33; 35,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,4; 175,3</t>
+          <t>12,96; 167,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 12,78</t>
+          <t>-49,55; 11,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,22; 3,51</t>
+          <t>-55,05; 2,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,24; 96,64</t>
+          <t>1,93; 96,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 9,68</t>
+          <t>-44,36; 4,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-48,0; 1,29</t>
+          <t>-46,2; -0,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,75; 104,16</t>
+          <t>19,82; 96,3</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,5</t>
+          <t>-4,3; 0,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -0,67</t>
+          <t>-5,13; -0,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,31</t>
+          <t>-0,65; 5,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 0,52</t>
+          <t>-4,52; 0,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,99</t>
+          <t>-3,12; 2,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,94</t>
+          <t>-1,81; 3,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -0,08</t>
+          <t>-3,62; -0,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,12</t>
+          <t>-3,34; 0,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,7</t>
+          <t>-0,45; 3,3</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 9,71</t>
+          <t>-47,79; 6,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,87; -10,73</t>
+          <t>-58,62; -11,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 63,91</t>
+          <t>-8,13; 80,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 6,51</t>
+          <t>-41,74; 7,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 22,5</t>
+          <t>-27,64; 27,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 35,16</t>
+          <t>-15,75; 36,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,05; 0,2</t>
+          <t>-37,98; -1,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 1,6</t>
+          <t>-35,68; 0,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 33,21</t>
+          <t>-5,05; 41,82</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,35</t>
+          <t>5,77</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,64</t>
+          <t>4,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,29</t>
+          <t>5,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,81</t>
+          <t>-3,22; 1,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; -0,31</t>
+          <t>-4,93; -0,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 10,13</t>
+          <t>2,81; 8,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,03</t>
+          <t>-5,23; 0,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 2,27</t>
+          <t>-3,84; 1,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,76</t>
+          <t>1,25; 7,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 0,33</t>
+          <t>-3,59; 0,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,18</t>
+          <t>-3,47; 0,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 5,96</t>
+          <t>2,91; 7,49</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105,38%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,11; 41,0</t>
+          <t>-45,07; 40,16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,4; -2,38</t>
+          <t>-65,22; -4,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38,61; 201,72</t>
+          <t>35,45; 185,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 0,16</t>
+          <t>-50,54; 3,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,22; 30,79</t>
+          <t>-36,43; 26,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 58,7</t>
+          <t>11,88; 102,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 5,66</t>
+          <t>-41,69; 5,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,99; 3,61</t>
+          <t>-40,07; 1,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 88,65</t>
+          <t>31,15; 112,23</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,34</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,4</t>
+          <t>-4,73; -0,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,91</t>
+          <t>-2,68; 1,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,81</t>
+          <t>-1,14; 4,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,06</t>
+          <t>-5,24; -0,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,42; -0,05</t>
+          <t>-5,3; 0,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,25</t>
+          <t>-1,22; 4,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; -0,76</t>
+          <t>-4,16; -0,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,03</t>
+          <t>-3,2; 0,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,18</t>
+          <t>-0,19; 3,37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -5,87</t>
+          <t>-54,22; -3,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 29,44</t>
+          <t>-31,56; 30,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 74,77</t>
+          <t>-13,26; 63,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,78; 1,14</t>
+          <t>-43,59; 0,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,43; -0,52</t>
+          <t>-43,96; 2,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 34,88</t>
+          <t>-10,15; 47,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,65; -9,08</t>
+          <t>-41,21; -8,89</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 0,76</t>
+          <t>-32,75; 4,73</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 37,71</t>
+          <t>-2,17; 39,57</t>
         </is>
       </c>
     </row>
@@ -1498,37 +1498,37 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>3,03</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>-2,27</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>-1,65</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-1,69</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>2,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-2,27</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,65</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-1,69</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,82; -0,43</t>
+          <t>-2,8; -0,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,95; -0,56</t>
+          <t>-2,94; -0,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,45</t>
+          <t>1,52; 4,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -0,89</t>
+          <t>-3,55; -0,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,4</t>
+          <t>-3,1; -0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,72</t>
+          <t>1,01; 3,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,73; -0,93</t>
+          <t>-2,83; -1,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,56; -0,66</t>
+          <t>-2,6; -0,81</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,21</t>
+          <t>1,71; 3,69</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-38,12; -7,04</t>
+          <t>-38,15; -5,65</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -8,06</t>
+          <t>-39,98; -11,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7,23; 72,31</t>
+          <t>21,28; 72,59</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-34,97; -9,92</t>
+          <t>-34,62; -10,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,87; -4,33</t>
+          <t>-29,98; -4,1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 30,11</t>
+          <t>9,45; 42,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -12,32</t>
+          <t>-32,55; -13,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-29,92; -8,68</t>
+          <t>-30,16; -10,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6,71; 41,67</t>
+          <t>19,52; 47,47</t>
         </is>
       </c>
     </row>
